--- a/model performance comparison/Amount_Cell_Media/Broeders 2015/Results/Fischer model_PHH.xlsx
+++ b/model performance comparison/Amount_Cell_Media/Broeders 2015/Results/Fischer model_PHH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\New dataset from SOT poster\Broeders 2015\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\Paper writing\R1\model comparison_update_based reviewer\New dataset from SOT poster\Broeders 2015\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFD2CB3-DF55-4250-BDA2-CC8F40CD4787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1929299B-469F-49AC-B2C6-C3C18E510BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1978,6 +1978,143 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -2065,12 +2202,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2097,137 +2228,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -14057,8 +14057,8 @@
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
@@ -14091,19 +14091,19 @@
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="118" t="s">
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="156" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="120"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="157"/>
+      <c r="Q2" s="158"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="7"/>
@@ -14127,17 +14127,17 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="122"/>
-      <c r="K3" s="122"/>
-      <c r="L3" s="122"/>
-      <c r="M3" s="122"/>
-      <c r="N3" s="122"/>
-      <c r="O3" s="122"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="123"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+      <c r="L3" s="160"/>
+      <c r="M3" s="160"/>
+      <c r="N3" s="160"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="160"/>
+      <c r="Q3" s="161"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
@@ -14161,17 +14161,17 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="124"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="125"/>
-      <c r="L4" s="125"/>
-      <c r="M4" s="125"/>
-      <c r="N4" s="125"/>
-      <c r="O4" s="125"/>
-      <c r="P4" s="125"/>
-      <c r="Q4" s="126"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+      <c r="I4" s="162"/>
+      <c r="J4" s="163"/>
+      <c r="K4" s="163"/>
+      <c r="L4" s="163"/>
+      <c r="M4" s="163"/>
+      <c r="N4" s="163"/>
+      <c r="O4" s="163"/>
+      <c r="P4" s="163"/>
+      <c r="Q4" s="164"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
@@ -14195,19 +14195,19 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="173"/>
-      <c r="I5" s="127" t="s">
+      <c r="G5" s="143"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="165" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="129"/>
+      <c r="J5" s="166"/>
+      <c r="K5" s="166"/>
+      <c r="L5" s="166"/>
+      <c r="M5" s="166"/>
+      <c r="N5" s="166"/>
+      <c r="O5" s="166"/>
+      <c r="P5" s="166"/>
+      <c r="Q5" s="167"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -14231,8 +14231,8 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="173"/>
-      <c r="H6" s="173"/>
+      <c r="G6" s="143"/>
+      <c r="H6" s="143"/>
       <c r="I6" s="50" t="s">
         <v>49</v>
       </c>
@@ -14242,14 +14242,14 @@
       <c r="K6" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="170" t="s">
+      <c r="L6" s="135" t="s">
         <v>39</v>
       </c>
-      <c r="M6" s="171"/>
-      <c r="N6" s="171"/>
-      <c r="O6" s="171"/>
-      <c r="P6" s="171"/>
-      <c r="Q6" s="172"/>
+      <c r="M6" s="136"/>
+      <c r="N6" s="136"/>
+      <c r="O6" s="136"/>
+      <c r="P6" s="136"/>
+      <c r="Q6" s="137"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
@@ -14273,8 +14273,8 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="173"/>
-      <c r="H7" s="173"/>
+      <c r="G7" s="143"/>
+      <c r="H7" s="143"/>
       <c r="I7" s="51" t="s">
         <v>20</v>
       </c>
@@ -14286,14 +14286,14 @@
         <f>J7/J7</f>
         <v>1</v>
       </c>
-      <c r="L7" s="164" t="s">
+      <c r="L7" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="M7" s="165"/>
-      <c r="N7" s="165"/>
-      <c r="O7" s="165"/>
-      <c r="P7" s="165"/>
-      <c r="Q7" s="166"/>
+      <c r="M7" s="119"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="119"/>
+      <c r="P7" s="119"/>
+      <c r="Q7" s="120"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
@@ -14312,15 +14312,15 @@
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7"/>
-      <c r="B8" s="145" t="s">
+      <c r="B8" s="181" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="146"/>
-      <c r="D8" s="146"/>
-      <c r="E8" s="146"/>
-      <c r="F8" s="147"/>
-      <c r="G8" s="173"/>
-      <c r="H8" s="173"/>
+      <c r="C8" s="182"/>
+      <c r="D8" s="182"/>
+      <c r="E8" s="182"/>
+      <c r="F8" s="183"/>
+      <c r="G8" s="143"/>
+      <c r="H8" s="143"/>
       <c r="I8" s="52" t="s">
         <v>6</v>
       </c>
@@ -14332,14 +14332,14 @@
         <f>J8/J7</f>
         <v>0.99957135230126803</v>
       </c>
-      <c r="L8" s="164" t="s">
+      <c r="L8" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="165"/>
-      <c r="N8" s="165"/>
-      <c r="O8" s="165"/>
-      <c r="P8" s="165"/>
-      <c r="Q8" s="166"/>
+      <c r="M8" s="119"/>
+      <c r="N8" s="119"/>
+      <c r="O8" s="119"/>
+      <c r="P8" s="119"/>
+      <c r="Q8" s="120"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
@@ -14358,13 +14358,13 @@
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="7"/>
-      <c r="B9" s="148"/>
-      <c r="C9" s="149"/>
-      <c r="D9" s="149"/>
-      <c r="E9" s="149"/>
-      <c r="F9" s="150"/>
-      <c r="G9" s="173"/>
-      <c r="H9" s="173"/>
+      <c r="B9" s="184"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="185"/>
+      <c r="E9" s="185"/>
+      <c r="F9" s="186"/>
+      <c r="G9" s="143"/>
+      <c r="H9" s="143"/>
       <c r="I9" s="51" t="s">
         <v>8</v>
       </c>
@@ -14376,14 +14376,14 @@
         <f>J9/J7</f>
         <v>3.2055393122561453E-4</v>
       </c>
-      <c r="L9" s="164" t="s">
+      <c r="L9" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="M9" s="165"/>
-      <c r="N9" s="165"/>
-      <c r="O9" s="165"/>
-      <c r="P9" s="165"/>
-      <c r="Q9" s="166"/>
+      <c r="M9" s="119"/>
+      <c r="N9" s="119"/>
+      <c r="O9" s="119"/>
+      <c r="P9" s="119"/>
+      <c r="Q9" s="120"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -14402,13 +14402,13 @@
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="7"/>
-      <c r="B10" s="151"/>
-      <c r="C10" s="152"/>
-      <c r="D10" s="152"/>
-      <c r="E10" s="152"/>
-      <c r="F10" s="153"/>
-      <c r="G10" s="173"/>
-      <c r="H10" s="173"/>
+      <c r="B10" s="187"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="188"/>
+      <c r="E10" s="188"/>
+      <c r="F10" s="189"/>
+      <c r="G10" s="143"/>
+      <c r="H10" s="143"/>
       <c r="I10" s="52" t="s">
         <v>9</v>
       </c>
@@ -14420,14 +14420,14 @@
         <f>J10/J7</f>
         <v>1.0809376750631187E-4</v>
       </c>
-      <c r="L10" s="164" t="s">
+      <c r="L10" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="M10" s="165"/>
-      <c r="N10" s="165"/>
-      <c r="O10" s="165"/>
-      <c r="P10" s="165"/>
-      <c r="Q10" s="166"/>
+      <c r="M10" s="119"/>
+      <c r="N10" s="119"/>
+      <c r="O10" s="119"/>
+      <c r="P10" s="119"/>
+      <c r="Q10" s="120"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
@@ -14446,24 +14446,24 @@
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="7"/>
-      <c r="B11" s="154" t="s">
+      <c r="B11" s="146" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="155"/>
-      <c r="D11" s="155"/>
-      <c r="E11" s="155"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="173"/>
-      <c r="H11" s="173"/>
-      <c r="I11" s="189"/>
-      <c r="J11" s="189"/>
-      <c r="K11" s="189"/>
-      <c r="L11" s="189"/>
-      <c r="M11" s="189"/>
-      <c r="N11" s="189"/>
-      <c r="O11" s="189"/>
-      <c r="P11" s="189"/>
-      <c r="Q11" s="189"/>
+      <c r="C11" s="147"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="148"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="134"/>
+      <c r="J11" s="134"/>
+      <c r="K11" s="134"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="134"/>
+      <c r="N11" s="134"/>
+      <c r="O11" s="134"/>
+      <c r="P11" s="134"/>
+      <c r="Q11" s="134"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
@@ -14482,13 +14482,13 @@
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7"/>
-      <c r="B12" s="157"/>
-      <c r="C12" s="158"/>
-      <c r="D12" s="158"/>
-      <c r="E12" s="158"/>
-      <c r="F12" s="159"/>
-      <c r="G12" s="173"/>
-      <c r="H12" s="173"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="150"/>
+      <c r="D12" s="150"/>
+      <c r="E12" s="150"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="143"/>
+      <c r="H12" s="143"/>
       <c r="I12" s="50" t="s">
         <v>51</v>
       </c>
@@ -14498,14 +14498,14 @@
       <c r="K12" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="L12" s="170" t="s">
+      <c r="L12" s="135" t="s">
         <v>39</v>
       </c>
-      <c r="M12" s="171"/>
-      <c r="N12" s="171"/>
-      <c r="O12" s="171"/>
-      <c r="P12" s="171"/>
-      <c r="Q12" s="172"/>
+      <c r="M12" s="136"/>
+      <c r="N12" s="136"/>
+      <c r="O12" s="136"/>
+      <c r="P12" s="136"/>
+      <c r="Q12" s="137"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
@@ -14524,17 +14524,17 @@
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="8"/>
-      <c r="B13" s="143" t="s">
+      <c r="B13" s="138" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="144"/>
-      <c r="D13" s="133" t="s">
+      <c r="C13" s="139"/>
+      <c r="D13" s="171" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="133"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="173"/>
-      <c r="H13" s="173"/>
+      <c r="E13" s="171"/>
+      <c r="F13" s="171"/>
+      <c r="G13" s="143"/>
+      <c r="H13" s="143"/>
       <c r="I13" s="51" t="s">
         <v>5</v>
       </c>
@@ -14546,14 +14546,14 @@
         <f>J13/J13</f>
         <v>1</v>
       </c>
-      <c r="L13" s="164" t="s">
+      <c r="L13" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="M13" s="165"/>
-      <c r="N13" s="165"/>
-      <c r="O13" s="165"/>
-      <c r="P13" s="165"/>
-      <c r="Q13" s="166"/>
+      <c r="M13" s="119"/>
+      <c r="N13" s="119"/>
+      <c r="O13" s="119"/>
+      <c r="P13" s="119"/>
+      <c r="Q13" s="120"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
       <c r="T13" s="7"/>
@@ -14578,13 +14578,13 @@
       <c r="C14" s="44">
         <v>2000</v>
       </c>
-      <c r="D14" s="134" t="s">
+      <c r="D14" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="134"/>
-      <c r="F14" s="134"/>
-      <c r="G14" s="173"/>
-      <c r="H14" s="173"/>
+      <c r="E14" s="172"/>
+      <c r="F14" s="172"/>
+      <c r="G14" s="143"/>
+      <c r="H14" s="143"/>
       <c r="I14" s="52" t="s">
         <v>43</v>
       </c>
@@ -14596,14 +14596,14 @@
         <f>J14/J13</f>
         <v>1</v>
       </c>
-      <c r="L14" s="167" t="s">
+      <c r="L14" s="140" t="s">
         <v>70</v>
       </c>
-      <c r="M14" s="168"/>
-      <c r="N14" s="168"/>
-      <c r="O14" s="168"/>
-      <c r="P14" s="168"/>
-      <c r="Q14" s="169"/>
+      <c r="M14" s="141"/>
+      <c r="N14" s="141"/>
+      <c r="O14" s="141"/>
+      <c r="P14" s="141"/>
+      <c r="Q14" s="142"/>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
@@ -14628,13 +14628,13 @@
       <c r="C15" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="135" t="s">
+      <c r="D15" s="173" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="135"/>
-      <c r="F15" s="135"/>
-      <c r="G15" s="173"/>
-      <c r="H15" s="173"/>
+      <c r="E15" s="173"/>
+      <c r="F15" s="173"/>
+      <c r="G15" s="143"/>
+      <c r="H15" s="143"/>
       <c r="I15" s="51" t="s">
         <v>44</v>
       </c>
@@ -14646,14 +14646,14 @@
         <f>J15/J13</f>
         <v>0</v>
       </c>
-      <c r="L15" s="164" t="s">
+      <c r="L15" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="M15" s="165"/>
-      <c r="N15" s="165"/>
-      <c r="O15" s="165"/>
-      <c r="P15" s="165"/>
-      <c r="Q15" s="166"/>
+      <c r="M15" s="119"/>
+      <c r="N15" s="119"/>
+      <c r="O15" s="119"/>
+      <c r="P15" s="119"/>
+      <c r="Q15" s="120"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
@@ -14678,13 +14678,13 @@
       <c r="C16" s="45">
         <v>1</v>
       </c>
-      <c r="D16" s="136" t="s">
+      <c r="D16" s="174" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="137"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="173"/>
-      <c r="H16" s="173"/>
+      <c r="E16" s="175"/>
+      <c r="F16" s="176"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="143"/>
       <c r="I16" s="52" t="s">
         <v>45</v>
       </c>
@@ -14696,14 +14696,14 @@
         <f>J16/J13</f>
         <v>0</v>
       </c>
-      <c r="L16" s="164" t="s">
+      <c r="L16" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="M16" s="165"/>
-      <c r="N16" s="165"/>
-      <c r="O16" s="165"/>
-      <c r="P16" s="165"/>
-      <c r="Q16" s="166"/>
+      <c r="M16" s="119"/>
+      <c r="N16" s="119"/>
+      <c r="O16" s="119"/>
+      <c r="P16" s="119"/>
+      <c r="Q16" s="120"/>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
@@ -14728,22 +14728,22 @@
       <c r="C17" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="139" t="s">
+      <c r="D17" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="140"/>
-      <c r="F17" s="141"/>
-      <c r="G17" s="173"/>
-      <c r="H17" s="173"/>
-      <c r="I17" s="167"/>
-      <c r="J17" s="168"/>
-      <c r="K17" s="168"/>
-      <c r="L17" s="168"/>
-      <c r="M17" s="168"/>
-      <c r="N17" s="168"/>
-      <c r="O17" s="168"/>
-      <c r="P17" s="168"/>
-      <c r="Q17" s="169"/>
+      <c r="E17" s="178"/>
+      <c r="F17" s="179"/>
+      <c r="G17" s="143"/>
+      <c r="H17" s="143"/>
+      <c r="I17" s="140"/>
+      <c r="J17" s="141"/>
+      <c r="K17" s="141"/>
+      <c r="L17" s="141"/>
+      <c r="M17" s="141"/>
+      <c r="N17" s="141"/>
+      <c r="O17" s="141"/>
+      <c r="P17" s="141"/>
+      <c r="Q17" s="142"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
@@ -14768,13 +14768,13 @@
       <c r="C18" s="45">
         <v>0</v>
       </c>
-      <c r="D18" s="136" t="s">
+      <c r="D18" s="174" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="137"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="173"/>
-      <c r="H18" s="173"/>
+      <c r="E18" s="175"/>
+      <c r="F18" s="176"/>
+      <c r="G18" s="143"/>
+      <c r="H18" s="143"/>
       <c r="I18" s="50" t="s">
         <v>29</v>
       </c>
@@ -14784,14 +14784,14 @@
       <c r="K18" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="L18" s="170" t="s">
+      <c r="L18" s="135" t="s">
         <v>39</v>
       </c>
-      <c r="M18" s="171"/>
-      <c r="N18" s="171"/>
-      <c r="O18" s="171"/>
-      <c r="P18" s="171"/>
-      <c r="Q18" s="172"/>
+      <c r="M18" s="136"/>
+      <c r="N18" s="136"/>
+      <c r="O18" s="136"/>
+      <c r="P18" s="136"/>
+      <c r="Q18" s="137"/>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
@@ -14810,13 +14810,13 @@
     </row>
     <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7"/>
-      <c r="B19" s="135"/>
-      <c r="C19" s="135"/>
-      <c r="D19" s="135"/>
-      <c r="E19" s="135"/>
-      <c r="F19" s="135"/>
-      <c r="G19" s="173"/>
-      <c r="H19" s="173"/>
+      <c r="B19" s="173"/>
+      <c r="C19" s="173"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="173"/>
+      <c r="F19" s="173"/>
+      <c r="G19" s="143"/>
+      <c r="H19" s="143"/>
       <c r="I19" s="51" t="s">
         <v>5</v>
       </c>
@@ -14828,14 +14828,14 @@
         <f>J19/J19</f>
         <v>1</v>
       </c>
-      <c r="L19" s="164" t="s">
+      <c r="L19" s="118" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="165"/>
-      <c r="N19" s="165"/>
-      <c r="O19" s="165"/>
-      <c r="P19" s="165"/>
-      <c r="Q19" s="166"/>
+      <c r="M19" s="119"/>
+      <c r="N19" s="119"/>
+      <c r="O19" s="119"/>
+      <c r="P19" s="119"/>
+      <c r="Q19" s="120"/>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
@@ -14854,17 +14854,17 @@
     </row>
     <row r="20" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="7"/>
-      <c r="B20" s="143" t="s">
+      <c r="B20" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="144"/>
-      <c r="D20" s="133" t="s">
+      <c r="C20" s="139"/>
+      <c r="D20" s="171" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="133"/>
-      <c r="F20" s="133"/>
-      <c r="G20" s="173"/>
-      <c r="H20" s="173"/>
+      <c r="E20" s="171"/>
+      <c r="F20" s="171"/>
+      <c r="G20" s="143"/>
+      <c r="H20" s="143"/>
       <c r="I20" s="52" t="s">
         <v>43</v>
       </c>
@@ -14876,14 +14876,14 @@
         <f>J20/J19</f>
         <v>0.87305569493226298</v>
       </c>
-      <c r="L20" s="164" t="s">
+      <c r="L20" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="M20" s="165"/>
-      <c r="N20" s="165"/>
-      <c r="O20" s="165"/>
-      <c r="P20" s="165"/>
-      <c r="Q20" s="166"/>
+      <c r="M20" s="119"/>
+      <c r="N20" s="119"/>
+      <c r="O20" s="119"/>
+      <c r="P20" s="119"/>
+      <c r="Q20" s="120"/>
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
@@ -14908,13 +14908,13 @@
       <c r="C21" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="139" t="s">
+      <c r="D21" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="140"/>
-      <c r="F21" s="141"/>
-      <c r="G21" s="173"/>
-      <c r="H21" s="173"/>
+      <c r="E21" s="178"/>
+      <c r="F21" s="179"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="143"/>
       <c r="I21" s="51" t="s">
         <v>44</v>
       </c>
@@ -14926,14 +14926,14 @@
         <f>J21/J19</f>
         <v>9.4932262920220778E-2</v>
       </c>
-      <c r="L21" s="164" t="s">
+      <c r="L21" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="M21" s="165"/>
-      <c r="N21" s="165"/>
-      <c r="O21" s="165"/>
-      <c r="P21" s="165"/>
-      <c r="Q21" s="166"/>
+      <c r="M21" s="119"/>
+      <c r="N21" s="119"/>
+      <c r="O21" s="119"/>
+      <c r="P21" s="119"/>
+      <c r="Q21" s="120"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
@@ -14958,13 +14958,13 @@
       <c r="C22" s="46">
         <v>2000000</v>
       </c>
-      <c r="D22" s="142" t="s">
+      <c r="D22" s="180" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="142"/>
-      <c r="F22" s="142"/>
-      <c r="G22" s="173"/>
-      <c r="H22" s="173"/>
+      <c r="E22" s="180"/>
+      <c r="F22" s="180"/>
+      <c r="G22" s="143"/>
+      <c r="H22" s="143"/>
       <c r="I22" s="53" t="s">
         <v>45</v>
       </c>
@@ -14976,14 +14976,14 @@
         <f>J22/J19</f>
         <v>3.2012042147516309E-2</v>
       </c>
-      <c r="L22" s="164" t="s">
+      <c r="L22" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="M22" s="165"/>
-      <c r="N22" s="165"/>
-      <c r="O22" s="165"/>
-      <c r="P22" s="165"/>
-      <c r="Q22" s="166"/>
+      <c r="M22" s="119"/>
+      <c r="N22" s="119"/>
+      <c r="O22" s="119"/>
+      <c r="P22" s="119"/>
+      <c r="Q22" s="120"/>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
@@ -15002,22 +15002,22 @@
     </row>
     <row r="23" spans="1:32" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="7"/>
-      <c r="B23" s="130"/>
-      <c r="C23" s="131"/>
-      <c r="D23" s="131"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="173"/>
-      <c r="H23" s="173"/>
-      <c r="I23" s="184"/>
-      <c r="J23" s="185"/>
-      <c r="K23" s="185"/>
-      <c r="L23" s="185"/>
-      <c r="M23" s="185"/>
-      <c r="N23" s="185"/>
-      <c r="O23" s="185"/>
-      <c r="P23" s="185"/>
-      <c r="Q23" s="186"/>
+      <c r="B23" s="168"/>
+      <c r="C23" s="169"/>
+      <c r="D23" s="169"/>
+      <c r="E23" s="169"/>
+      <c r="F23" s="170"/>
+      <c r="G23" s="143"/>
+      <c r="H23" s="143"/>
+      <c r="I23" s="129"/>
+      <c r="J23" s="130"/>
+      <c r="K23" s="130"/>
+      <c r="L23" s="130"/>
+      <c r="M23" s="130"/>
+      <c r="N23" s="130"/>
+      <c r="O23" s="130"/>
+      <c r="P23" s="130"/>
+      <c r="Q23" s="131"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
@@ -15036,26 +15036,26 @@
     </row>
     <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="7"/>
-      <c r="B24" s="154" t="s">
+      <c r="B24" s="146" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="155"/>
-      <c r="D24" s="155"/>
-      <c r="E24" s="155"/>
-      <c r="F24" s="156"/>
-      <c r="G24" s="173"/>
-      <c r="H24" s="173"/>
-      <c r="I24" s="178" t="s">
+      <c r="C24" s="147"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="147"/>
+      <c r="F24" s="148"/>
+      <c r="G24" s="143"/>
+      <c r="H24" s="143"/>
+      <c r="I24" s="123" t="s">
         <v>42</v>
       </c>
-      <c r="J24" s="179"/>
-      <c r="K24" s="179"/>
-      <c r="L24" s="179"/>
-      <c r="M24" s="179"/>
-      <c r="N24" s="179"/>
-      <c r="O24" s="179"/>
-      <c r="P24" s="179"/>
-      <c r="Q24" s="180"/>
+      <c r="J24" s="124"/>
+      <c r="K24" s="124"/>
+      <c r="L24" s="124"/>
+      <c r="M24" s="124"/>
+      <c r="N24" s="124"/>
+      <c r="O24" s="124"/>
+      <c r="P24" s="124"/>
+      <c r="Q24" s="125"/>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
@@ -15074,22 +15074,22 @@
     </row>
     <row r="25" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7"/>
-      <c r="B25" s="157"/>
-      <c r="C25" s="158"/>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="159"/>
-      <c r="G25" s="173"/>
-      <c r="H25" s="173"/>
-      <c r="I25" s="181"/>
-      <c r="J25" s="182"/>
-      <c r="K25" s="182"/>
-      <c r="L25" s="182"/>
-      <c r="M25" s="182"/>
-      <c r="N25" s="182"/>
-      <c r="O25" s="182"/>
-      <c r="P25" s="182"/>
-      <c r="Q25" s="183"/>
+      <c r="B25" s="149"/>
+      <c r="C25" s="150"/>
+      <c r="D25" s="150"/>
+      <c r="E25" s="150"/>
+      <c r="F25" s="151"/>
+      <c r="G25" s="143"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="126"/>
+      <c r="J25" s="127"/>
+      <c r="K25" s="127"/>
+      <c r="L25" s="127"/>
+      <c r="M25" s="127"/>
+      <c r="N25" s="127"/>
+      <c r="O25" s="127"/>
+      <c r="P25" s="127"/>
+      <c r="Q25" s="128"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -15108,48 +15108,48 @@
     </row>
     <row r="26" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="7"/>
-      <c r="B26" s="176" t="s">
+      <c r="B26" s="144" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="176" t="s">
+      <c r="C26" s="144" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="160" t="s">
+      <c r="D26" s="152" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="160" t="s">
+      <c r="E26" s="152" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="162" t="s">
+      <c r="F26" s="154" t="s">
         <v>66</v>
       </c>
-      <c r="G26" s="173"/>
-      <c r="H26" s="173"/>
-      <c r="I26" s="187" t="s">
+      <c r="G26" s="143"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="132" t="s">
         <v>53</v>
       </c>
-      <c r="J26" s="187" t="s">
+      <c r="J26" s="132" t="s">
         <v>54</v>
       </c>
-      <c r="K26" s="174" t="s">
+      <c r="K26" s="121" t="s">
         <v>74</v>
       </c>
-      <c r="L26" s="174" t="s">
+      <c r="L26" s="121" t="s">
         <v>52</v>
       </c>
-      <c r="M26" s="174" t="s">
+      <c r="M26" s="121" t="s">
         <v>59</v>
       </c>
-      <c r="N26" s="174" t="s">
+      <c r="N26" s="121" t="s">
         <v>62</v>
       </c>
-      <c r="O26" s="174" t="s">
+      <c r="O26" s="121" t="s">
         <v>73</v>
       </c>
-      <c r="P26" s="174" t="s">
+      <c r="P26" s="121" t="s">
         <v>64</v>
       </c>
-      <c r="Q26" s="174" t="s">
+      <c r="Q26" s="121" t="s">
         <v>65</v>
       </c>
       <c r="R26" s="9"/>
@@ -15170,22 +15170,22 @@
     </row>
     <row r="27" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="7"/>
-      <c r="B27" s="177"/>
-      <c r="C27" s="177"/>
-      <c r="D27" s="161"/>
-      <c r="E27" s="161"/>
-      <c r="F27" s="163"/>
-      <c r="G27" s="173"/>
-      <c r="H27" s="173"/>
-      <c r="I27" s="188"/>
-      <c r="J27" s="188"/>
-      <c r="K27" s="175"/>
-      <c r="L27" s="175"/>
-      <c r="M27" s="175"/>
-      <c r="N27" s="175"/>
-      <c r="O27" s="175"/>
-      <c r="P27" s="175"/>
-      <c r="Q27" s="175"/>
+      <c r="B27" s="145"/>
+      <c r="C27" s="145"/>
+      <c r="D27" s="153"/>
+      <c r="E27" s="153"/>
+      <c r="F27" s="155"/>
+      <c r="G27" s="143"/>
+      <c r="H27" s="143"/>
+      <c r="I27" s="133"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="122"/>
+      <c r="L27" s="122"/>
+      <c r="M27" s="122"/>
+      <c r="N27" s="122"/>
+      <c r="O27" s="122"/>
+      <c r="P27" s="122"/>
+      <c r="Q27" s="122"/>
       <c r="R27" s="7" t="s">
         <v>84</v>
       </c>
@@ -15215,51 +15215,51 @@
         <v>86</v>
       </c>
       <c r="D28" s="48">
-        <v>4.1575040000000012</v>
+        <v>2.8380318246143235</v>
       </c>
       <c r="E28" s="48">
-        <v>5.2456879999999995</v>
+        <v>3.5597354124795313</v>
       </c>
       <c r="F28" s="103">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G28" s="173"/>
-      <c r="H28" s="173"/>
+      <c r="G28" s="143"/>
+      <c r="H28" s="143"/>
       <c r="I28" s="99">
         <f t="shared" ref="I28:I47" si="1">IF(D28=0,"",LOG($K$15*10^D28+$K$16*10^E28+$K$14))</f>
         <v>0</v>
       </c>
       <c r="J28" s="99">
         <f t="shared" ref="J28:J47" si="2">IF(D28=0,"",LOG($K$21*10^D28+$K$22*10^E28+$K$20))</f>
-        <v>3.8451968315167888</v>
+        <v>2.2610512104398017</v>
       </c>
       <c r="K28" s="100">
         <f t="shared" ref="K28:K47" si="3">IF(D28=0,"",1/(1+10^D28*$J$15/$J$14+10^E28*$J$16/$J$14+10^J28*$J$19/$J$14))</f>
-        <v>4.044964539361115E-2</v>
+        <v>0.61803666811191871</v>
       </c>
       <c r="L28" s="100">
         <f t="shared" ref="L28:L47" si="4">IF(D28=0,"",1/(1+10^I28/10^J28*$J$13/$J$19))</f>
-        <v>0.95955035460638871</v>
+        <v>0.38196333188808135</v>
       </c>
       <c r="M28" s="100">
         <f t="shared" ref="M28:M47" si="5">IF(D28=0,"",1-L28)</f>
-        <v>4.0449645393611289E-2</v>
+        <v>0.61803666811191871</v>
       </c>
       <c r="N28" s="100">
         <f t="shared" ref="N28:N47" si="6">IF(D28=0,"",1/(1/10^E28*$J$20/$J$22+10^D28/10^E28*$J$21/$J$22+10^I28/10^E28*$J$13/$J$22+1))</f>
-        <v>0.77245345279604383</v>
+        <v>0.24323118470116536</v>
       </c>
       <c r="O28" s="41">
         <f t="shared" ref="O28:O47" si="7">IF(D28=0,"",F28*K28*$J$7/$J$14)</f>
-        <v>4.0586692837169241E-8</v>
+        <v>6.2013063814714865E-7</v>
       </c>
       <c r="P28" s="41">
         <f t="shared" ref="P28:P47" si="8">IF(D28=0,"",O28*10^J28)</f>
-        <v>2.8417148465595193E-4</v>
+        <v>1.131186983420948E-4</v>
       </c>
       <c r="Q28" s="41">
         <f t="shared" ref="Q28:Q47" si="9">IF(D28=0,"",F28*N28*$J$7/$J$22)</f>
-        <v>7.1461423781989872E-3</v>
+        <v>2.2501869470592972E-3</v>
       </c>
       <c r="R28" s="9">
         <f>F28*0.002*1000000</f>
@@ -15267,9 +15267,12 @@
       </c>
       <c r="S28" s="11">
         <f>R28*L28</f>
-        <v>1.9191007092127775E-3</v>
-      </c>
-      <c r="T28" s="9"/>
+        <v>7.6392666377616267E-4</v>
+      </c>
+      <c r="T28" s="9">
+        <f>R28*M28</f>
+        <v>1.2360733362238375E-3</v>
+      </c>
       <c r="U28" s="7"/>
       <c r="V28" s="7"/>
       <c r="W28" s="7"/>
@@ -15290,8 +15293,8 @@
       <c r="D29" s="48"/>
       <c r="E29" s="48"/>
       <c r="F29" s="103"/>
-      <c r="G29" s="173"/>
-      <c r="H29" s="173"/>
+      <c r="G29" s="143"/>
+      <c r="H29" s="143"/>
       <c r="I29" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15351,8 +15354,8 @@
       <c r="D30" s="95"/>
       <c r="E30" s="95"/>
       <c r="F30" s="103"/>
-      <c r="G30" s="173"/>
-      <c r="H30" s="173"/>
+      <c r="G30" s="143"/>
+      <c r="H30" s="143"/>
       <c r="I30" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15412,8 +15415,8 @@
       <c r="D31" s="48"/>
       <c r="E31" s="48"/>
       <c r="F31" s="98"/>
-      <c r="G31" s="173"/>
-      <c r="H31" s="173"/>
+      <c r="G31" s="143"/>
+      <c r="H31" s="143"/>
       <c r="I31" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15473,8 +15476,8 @@
       <c r="D32" s="48"/>
       <c r="E32" s="48"/>
       <c r="F32" s="98"/>
-      <c r="G32" s="173"/>
-      <c r="H32" s="173"/>
+      <c r="G32" s="143"/>
+      <c r="H32" s="143"/>
       <c r="I32" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15534,8 +15537,8 @@
       <c r="D33" s="102"/>
       <c r="E33" s="102"/>
       <c r="F33" s="98"/>
-      <c r="G33" s="173"/>
-      <c r="H33" s="173"/>
+      <c r="G33" s="143"/>
+      <c r="H33" s="143"/>
       <c r="I33" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15595,8 +15598,8 @@
       <c r="D34" s="95"/>
       <c r="E34" s="95"/>
       <c r="F34" s="98"/>
-      <c r="G34" s="173"/>
-      <c r="H34" s="173"/>
+      <c r="G34" s="143"/>
+      <c r="H34" s="143"/>
       <c r="I34" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15656,8 +15659,8 @@
       <c r="D35" s="95"/>
       <c r="E35" s="95"/>
       <c r="F35" s="96"/>
-      <c r="G35" s="173"/>
-      <c r="H35" s="173"/>
+      <c r="G35" s="143"/>
+      <c r="H35" s="143"/>
       <c r="I35" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15717,8 +15720,8 @@
       <c r="D36" s="48"/>
       <c r="E36" s="48"/>
       <c r="F36" s="96"/>
-      <c r="G36" s="173"/>
-      <c r="H36" s="173"/>
+      <c r="G36" s="143"/>
+      <c r="H36" s="143"/>
       <c r="I36" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15778,8 +15781,8 @@
       <c r="D37" s="102"/>
       <c r="E37" s="102"/>
       <c r="F37" s="96"/>
-      <c r="G37" s="173"/>
-      <c r="H37" s="173"/>
+      <c r="G37" s="143"/>
+      <c r="H37" s="143"/>
       <c r="I37" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15839,8 +15842,8 @@
       <c r="D38" s="95"/>
       <c r="E38" s="95"/>
       <c r="F38" s="96"/>
-      <c r="G38" s="173"/>
-      <c r="H38" s="173"/>
+      <c r="G38" s="143"/>
+      <c r="H38" s="143"/>
       <c r="I38" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15900,8 +15903,8 @@
       <c r="D39" s="95"/>
       <c r="E39" s="95"/>
       <c r="F39" s="96"/>
-      <c r="G39" s="173"/>
-      <c r="H39" s="173"/>
+      <c r="G39" s="143"/>
+      <c r="H39" s="143"/>
       <c r="I39" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15961,8 +15964,8 @@
       <c r="D40" s="48"/>
       <c r="E40" s="48"/>
       <c r="F40" s="96"/>
-      <c r="G40" s="173"/>
-      <c r="H40" s="173"/>
+      <c r="G40" s="143"/>
+      <c r="H40" s="143"/>
       <c r="I40" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16022,8 +16025,8 @@
       <c r="D41" s="102"/>
       <c r="E41" s="102"/>
       <c r="F41" s="96"/>
-      <c r="G41" s="173"/>
-      <c r="H41" s="173"/>
+      <c r="G41" s="143"/>
+      <c r="H41" s="143"/>
       <c r="I41" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16083,8 +16086,8 @@
       <c r="D42" s="95"/>
       <c r="E42" s="95"/>
       <c r="F42" s="96"/>
-      <c r="G42" s="173"/>
-      <c r="H42" s="173"/>
+      <c r="G42" s="143"/>
+      <c r="H42" s="143"/>
       <c r="I42" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16144,8 +16147,8 @@
       <c r="D43" s="95"/>
       <c r="E43" s="95"/>
       <c r="F43" s="96"/>
-      <c r="G43" s="173"/>
-      <c r="H43" s="173"/>
+      <c r="G43" s="143"/>
+      <c r="H43" s="143"/>
       <c r="I43" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16205,8 +16208,8 @@
       <c r="D44" s="95"/>
       <c r="E44" s="95"/>
       <c r="F44" s="96"/>
-      <c r="G44" s="173"/>
-      <c r="H44" s="173"/>
+      <c r="G44" s="143"/>
+      <c r="H44" s="143"/>
       <c r="I44" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16266,8 +16269,8 @@
       <c r="D45" s="95"/>
       <c r="E45" s="95"/>
       <c r="F45" s="96"/>
-      <c r="G45" s="173"/>
-      <c r="H45" s="173"/>
+      <c r="G45" s="143"/>
+      <c r="H45" s="143"/>
       <c r="I45" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16327,8 +16330,8 @@
       <c r="D46" s="97"/>
       <c r="E46" s="97"/>
       <c r="F46" s="96"/>
-      <c r="G46" s="173"/>
-      <c r="H46" s="173"/>
+      <c r="G46" s="143"/>
+      <c r="H46" s="143"/>
       <c r="I46" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16388,8 +16391,8 @@
       <c r="D47" s="95"/>
       <c r="E47" s="95"/>
       <c r="F47" s="96"/>
-      <c r="G47" s="173"/>
-      <c r="H47" s="173"/>
+      <c r="G47" s="143"/>
+      <c r="H47" s="143"/>
       <c r="I47" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16449,8 +16452,8 @@
       <c r="D48" s="95"/>
       <c r="E48" s="95"/>
       <c r="F48" s="96"/>
-      <c r="G48" s="173"/>
-      <c r="H48" s="173"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="143"/>
       <c r="I48" s="99" t="str">
         <f t="shared" ref="I48:I50" si="10">IF(D48=0,"",LOG($K$15*10^D48+$K$16*10^E48+$K$14))</f>
         <v/>
@@ -16510,8 +16513,8 @@
       <c r="D49" s="95"/>
       <c r="E49" s="95"/>
       <c r="F49" s="96"/>
-      <c r="G49" s="173"/>
-      <c r="H49" s="173"/>
+      <c r="G49" s="143"/>
+      <c r="H49" s="143"/>
       <c r="I49" s="99" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -16571,8 +16574,8 @@
       <c r="D50" s="95"/>
       <c r="E50" s="95"/>
       <c r="F50" s="96"/>
-      <c r="G50" s="173"/>
-      <c r="H50" s="173"/>
+      <c r="G50" s="143"/>
+      <c r="H50" s="143"/>
       <c r="I50" s="99" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -16632,8 +16635,8 @@
       <c r="D51" s="95"/>
       <c r="E51" s="95"/>
       <c r="F51" s="96"/>
-      <c r="G51" s="173"/>
-      <c r="H51" s="173"/>
+      <c r="G51" s="143"/>
+      <c r="H51" s="143"/>
       <c r="I51" s="99" t="str">
         <f t="shared" ref="I51:I70" si="19">IF(D51=0,"",LOG($K$15*10^D51+$K$16*10^E51+$K$14))</f>
         <v/>
@@ -16693,8 +16696,8 @@
       <c r="D52" s="48"/>
       <c r="E52" s="48"/>
       <c r="F52" s="96"/>
-      <c r="G52" s="173"/>
-      <c r="H52" s="173"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="143"/>
       <c r="I52" s="99" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -16754,8 +16757,8 @@
       <c r="D53" s="48"/>
       <c r="E53" s="48"/>
       <c r="F53" s="96"/>
-      <c r="G53" s="173"/>
-      <c r="H53" s="173"/>
+      <c r="G53" s="143"/>
+      <c r="H53" s="143"/>
       <c r="I53" s="99" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -16815,8 +16818,8 @@
       <c r="D54" s="48"/>
       <c r="E54" s="48"/>
       <c r="F54" s="96"/>
-      <c r="G54" s="173"/>
-      <c r="H54" s="173"/>
+      <c r="G54" s="143"/>
+      <c r="H54" s="143"/>
       <c r="I54" s="99" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -16876,8 +16879,8 @@
       <c r="D55" s="48"/>
       <c r="E55" s="48"/>
       <c r="F55" s="58"/>
-      <c r="G55" s="173"/>
-      <c r="H55" s="173"/>
+      <c r="G55" s="143"/>
+      <c r="H55" s="143"/>
       <c r="I55" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -16937,8 +16940,8 @@
       <c r="D56" s="48"/>
       <c r="E56" s="48"/>
       <c r="F56" s="58"/>
-      <c r="G56" s="173"/>
-      <c r="H56" s="173"/>
+      <c r="G56" s="143"/>
+      <c r="H56" s="143"/>
       <c r="I56" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -16998,8 +17001,8 @@
       <c r="D57" s="95"/>
       <c r="E57" s="95"/>
       <c r="F57" s="96"/>
-      <c r="G57" s="173"/>
-      <c r="H57" s="173"/>
+      <c r="G57" s="143"/>
+      <c r="H57" s="143"/>
       <c r="I57" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17059,8 +17062,8 @@
       <c r="D58" s="48"/>
       <c r="E58" s="48"/>
       <c r="F58" s="58"/>
-      <c r="G58" s="173"/>
-      <c r="H58" s="173"/>
+      <c r="G58" s="143"/>
+      <c r="H58" s="143"/>
       <c r="I58" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17120,8 +17123,8 @@
       <c r="D59" s="48"/>
       <c r="E59" s="48"/>
       <c r="F59" s="58"/>
-      <c r="G59" s="173"/>
-      <c r="H59" s="173"/>
+      <c r="G59" s="143"/>
+      <c r="H59" s="143"/>
       <c r="I59" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17181,8 +17184,8 @@
       <c r="D60" s="48"/>
       <c r="E60" s="48"/>
       <c r="F60" s="58"/>
-      <c r="G60" s="173"/>
-      <c r="H60" s="173"/>
+      <c r="G60" s="143"/>
+      <c r="H60" s="143"/>
       <c r="I60" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17242,8 +17245,8 @@
       <c r="D61" s="48"/>
       <c r="E61" s="48"/>
       <c r="F61" s="58"/>
-      <c r="G61" s="173"/>
-      <c r="H61" s="173"/>
+      <c r="G61" s="143"/>
+      <c r="H61" s="143"/>
       <c r="I61" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17303,8 +17306,8 @@
       <c r="D62" s="48"/>
       <c r="E62" s="48"/>
       <c r="F62" s="58"/>
-      <c r="G62" s="173"/>
-      <c r="H62" s="173"/>
+      <c r="G62" s="143"/>
+      <c r="H62" s="143"/>
       <c r="I62" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17364,8 +17367,8 @@
       <c r="D63" s="48"/>
       <c r="E63" s="48"/>
       <c r="F63" s="58"/>
-      <c r="G63" s="173"/>
-      <c r="H63" s="173"/>
+      <c r="G63" s="143"/>
+      <c r="H63" s="143"/>
       <c r="I63" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17425,8 +17428,8 @@
       <c r="D64" s="48"/>
       <c r="E64" s="48"/>
       <c r="F64" s="58"/>
-      <c r="G64" s="173"/>
-      <c r="H64" s="173"/>
+      <c r="G64" s="143"/>
+      <c r="H64" s="143"/>
       <c r="I64" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17486,8 +17489,8 @@
       <c r="D65" s="48"/>
       <c r="E65" s="48"/>
       <c r="F65" s="58"/>
-      <c r="G65" s="173"/>
-      <c r="H65" s="173"/>
+      <c r="G65" s="143"/>
+      <c r="H65" s="143"/>
       <c r="I65" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17547,8 +17550,8 @@
       <c r="D66" s="48"/>
       <c r="E66" s="48"/>
       <c r="F66" s="58"/>
-      <c r="G66" s="173"/>
-      <c r="H66" s="173"/>
+      <c r="G66" s="143"/>
+      <c r="H66" s="143"/>
       <c r="I66" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17608,8 +17611,8 @@
       <c r="D67" s="48"/>
       <c r="E67" s="48"/>
       <c r="F67" s="58"/>
-      <c r="G67" s="173"/>
-      <c r="H67" s="173"/>
+      <c r="G67" s="143"/>
+      <c r="H67" s="143"/>
       <c r="I67" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17669,8 +17672,8 @@
       <c r="D68" s="48"/>
       <c r="E68" s="48"/>
       <c r="F68" s="58"/>
-      <c r="G68" s="173"/>
-      <c r="H68" s="173"/>
+      <c r="G68" s="143"/>
+      <c r="H68" s="143"/>
       <c r="I68" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17730,8 +17733,8 @@
       <c r="D69" s="48"/>
       <c r="E69" s="48"/>
       <c r="F69" s="58"/>
-      <c r="G69" s="173"/>
-      <c r="H69" s="173"/>
+      <c r="G69" s="143"/>
+      <c r="H69" s="143"/>
       <c r="I69" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17791,8 +17794,8 @@
       <c r="D70" s="48"/>
       <c r="E70" s="48"/>
       <c r="F70" s="58"/>
-      <c r="G70" s="173"/>
-      <c r="H70" s="173"/>
+      <c r="G70" s="143"/>
+      <c r="H70" s="143"/>
       <c r="I70" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17852,8 +17855,8 @@
       <c r="D71" s="48"/>
       <c r="E71" s="48"/>
       <c r="F71" s="58"/>
-      <c r="G71" s="173"/>
-      <c r="H71" s="173"/>
+      <c r="G71" s="143"/>
+      <c r="H71" s="143"/>
       <c r="I71" s="55" t="str">
         <f t="shared" ref="I71:I122" si="28">IF(D71=0,"",LOG($K$15*10^D71+$K$16*10^E71+$K$14))</f>
         <v/>
@@ -17913,8 +17916,8 @@
       <c r="D72" s="48"/>
       <c r="E72" s="48"/>
       <c r="F72" s="58"/>
-      <c r="G72" s="173"/>
-      <c r="H72" s="173"/>
+      <c r="G72" s="143"/>
+      <c r="H72" s="143"/>
       <c r="I72" s="55" t="str">
         <f t="shared" si="28"/>
         <v/>
@@ -17974,8 +17977,8 @@
       <c r="D73" s="48"/>
       <c r="E73" s="48"/>
       <c r="F73" s="58"/>
-      <c r="G73" s="173"/>
-      <c r="H73" s="173"/>
+      <c r="G73" s="143"/>
+      <c r="H73" s="143"/>
       <c r="I73" s="55" t="str">
         <f t="shared" si="28"/>
         <v/>
@@ -18035,8 +18038,8 @@
       <c r="D74" s="48"/>
       <c r="E74" s="48"/>
       <c r="F74" s="58"/>
-      <c r="G74" s="173"/>
-      <c r="H74" s="173"/>
+      <c r="G74" s="143"/>
+      <c r="H74" s="143"/>
       <c r="I74" s="55" t="str">
         <f t="shared" si="28"/>
         <v/>
@@ -18096,8 +18099,8 @@
       <c r="D75" s="48"/>
       <c r="E75" s="48"/>
       <c r="F75" s="58"/>
-      <c r="G75" s="173"/>
-      <c r="H75" s="173"/>
+      <c r="G75" s="143"/>
+      <c r="H75" s="143"/>
       <c r="I75" s="55" t="str">
         <f t="shared" si="28"/>
         <v/>
@@ -18157,8 +18160,8 @@
       <c r="D76" s="48"/>
       <c r="E76" s="48"/>
       <c r="F76" s="58"/>
-      <c r="G76" s="173"/>
-      <c r="H76" s="173"/>
+      <c r="G76" s="143"/>
+      <c r="H76" s="143"/>
       <c r="I76" s="55" t="str">
         <f t="shared" si="28"/>
         <v/>
@@ -18218,8 +18221,8 @@
       <c r="D77" s="48"/>
       <c r="E77" s="48"/>
       <c r="F77" s="58"/>
-      <c r="G77" s="173"/>
-      <c r="H77" s="173"/>
+      <c r="G77" s="143"/>
+      <c r="H77" s="143"/>
       <c r="I77" s="55" t="str">
         <f t="shared" si="28"/>
         <v/>
@@ -24932,21 +24935,27 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="L8:Q8"/>
-    <mergeCell ref="L9:Q9"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="I24:Q25"/>
-    <mergeCell ref="I23:Q23"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="L10:Q10"/>
-    <mergeCell ref="I11:Q11"/>
-    <mergeCell ref="L12:Q12"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="I2:Q4"/>
+    <mergeCell ref="I5:Q5"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B8:F10"/>
+    <mergeCell ref="B11:F12"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="L19:Q19"/>
+    <mergeCell ref="L20:Q20"/>
+    <mergeCell ref="L21:Q21"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="L14:Q14"/>
     <mergeCell ref="L15:Q15"/>
@@ -24963,27 +24972,21 @@
     <mergeCell ref="I17:Q17"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="L19:Q19"/>
-    <mergeCell ref="L20:Q20"/>
-    <mergeCell ref="L21:Q21"/>
-    <mergeCell ref="I2:Q4"/>
-    <mergeCell ref="I5:Q5"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B8:F10"/>
-    <mergeCell ref="B11:F12"/>
+    <mergeCell ref="L8:Q8"/>
+    <mergeCell ref="L9:Q9"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="I24:Q25"/>
+    <mergeCell ref="I23:Q23"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L10:Q10"/>
+    <mergeCell ref="I11:Q11"/>
+    <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="M26:M27"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
